--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12510" yWindow="0" windowWidth="12780" windowHeight="16170" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="nc2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nc3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -918,7 +919,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1274,4 +1275,369 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>261</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31.48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>249</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>243</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>33.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82.67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>728</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>103</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64.56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>97</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>472</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>310</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>821</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>730</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1164</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12510" yWindow="0" windowWidth="12780" windowHeight="16170" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="nc2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="nc3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nc4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -438,7 +439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -919,7 +920,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1284,7 +1285,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1640,4 +1641,367 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>因公出差</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>329</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19.43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>62.74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>198</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38.38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>537</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>77</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>62.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>133</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>55.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>536</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>252</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33.24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>789</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>460</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12510" yWindow="0" windowWidth="12780" windowHeight="16170" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="nc2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="nc3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="nc4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nc5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -439,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -920,7 +921,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1285,7 +1286,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1650,7 +1651,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2004,4 +2005,369 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>182</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>567</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>169</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1064</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>239</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37.71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>119</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>486</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1040</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>786</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>265</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,6 +11,7 @@
     <sheet name="nc3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="nc4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="nc5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nc6" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2370,4 +2371,369 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>224</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>444</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>189</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>257</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>255</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>649</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>544</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>186</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>871</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>472</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>475</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>482</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="nc4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="nc5" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="nc6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="nc7" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2736,4 +2737,369 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>151</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.88</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>214</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>217</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>441</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>337</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>368</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38.96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>97.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>720</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>442</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>921</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>155</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>46.46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>362</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="nc5" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="nc6" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="nc7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="nc8" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3102,4 +3103,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68.95999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>284</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>145</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50.67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>125</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>52.89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>482</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>594</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55.67</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>27.87</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>740</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>810</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>152</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>49.89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1247</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="1" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="nc6" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="nc7" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="nc8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="nc9" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3469,4 +3470,370 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>196</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>279</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>257</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>272</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>564</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>905</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>572</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>125</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>552</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>476</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1062</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>706</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="1" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="1" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="nc7" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="nc8" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="nc9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="nc10" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -918,6 +919,371 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>得分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>262</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>212</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32.42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>因公出差</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>365</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1044</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>81.23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>235</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>313</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>456</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>441</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>438</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/nowcoder_contest.xlsx
+++ b/data/nowcoder_contest.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" tabRatio="600" firstSheet="1" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="10480" tabRatio="600" firstSheet="1" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="nc1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="nc2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="nc3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="nc4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="nc5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="nc6" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="nc7" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="nc8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="nc9" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="nc10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nc10" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="23">
     <font>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -43,12 +43,164 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +213,194 @@
         <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -70,18 +408,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -434,7 +1066,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -445,46 +1076,45 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>过题数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>学校</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>过题数</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>罚时</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -493,425 +1123,404 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>橙雨星瞳</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>橙雨星瞳</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
+      <c r="E2" t="n">
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G2" t="n">
-        <v>54.44</v>
+        <v>46.53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>我的青春算竞物语果然有问题</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>我的青春算竞物语果然有问题</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
+      <c r="E3" t="n">
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G3" t="n">
-        <v>35.46</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>二阶堂艾玛</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>二阶堂艾玛</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
+      <c r="E4" t="n">
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G4" t="n">
-        <v>28.06</v>
+        <v>33.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>不是清北一队</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>不是清北一队</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
+      <c r="E5" t="n">
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G5" t="n">
-        <v>26.3</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>三只企鹅！</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>三只企鹅！</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="E6" t="n">
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G6" t="n">
-        <v>16.67</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>超时空代码姬</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>384</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>超时空代码姬</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
+      <c r="E7" t="n">
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G7" t="n">
-        <v>16.07</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SEISHUN://NO_HACKING</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>402</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SEISHUN://NO_HACKING</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
+      <c r="E8" t="n">
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G8" t="n">
-        <v>14.74</v>
+        <v>24.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>TheBadBatch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TheBadBatch</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+      <c r="E9" t="n">
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G9" t="n">
-        <v>9.33</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>永远别放弃</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>488</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>永远别放弃</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+      <c r="E10" t="n">
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G10" t="n">
-        <v>8.369999999999999</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>重生之忘带前世记忆打acm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>重生之忘带前世记忆打acm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+      <c r="E11" t="n">
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>ClosedClaw1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ClosedClaw1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="E12" t="n">
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>疑似mygo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>疑似mygo</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
+      <c r="E13" t="n">
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>nullPointerException</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>北京邮电大学</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nullPointerException</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>北京邮电大学</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>1586</v>
       </c>
       <c r="G14" t="n">
-        <v>33.06</v>
+        <v>35.28</v>
       </c>
     </row>
   </sheetData>
@@ -925,8 +1534,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -963,6 +1572,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>得分</t>
         </is>
       </c>
@@ -985,10 +1599,13 @@
         <v>262</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>28.25</v>
+        <v>1203</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.09</v>
       </c>
     </row>
     <row r="3">
@@ -1009,10 +1626,13 @@
         <v>212</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>32.42</v>
+        <v>1203</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25.37</v>
       </c>
     </row>
     <row r="4">
@@ -1033,10 +1653,13 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>46.15</v>
+        <v>1203</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.44</v>
       </c>
     </row>
     <row r="5">
@@ -1056,9 +1679,12 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1080,10 +1706,13 @@
         <v>378</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>18.58</v>
+        <v>1203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.13</v>
       </c>
     </row>
     <row r="7">
@@ -1104,10 +1733,13 @@
         <v>365</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>19.67</v>
+        <v>1203</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21.46</v>
       </c>
     </row>
     <row r="8">
@@ -1128,10 +1760,13 @@
         <v>1044</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1203</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">
@@ -1152,10 +1787,13 @@
         <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>81.23</v>
+        <v>1203</v>
+      </c>
+      <c r="G9" t="n">
+        <v>51.92</v>
       </c>
     </row>
     <row r="10">
@@ -1176,10 +1814,13 @@
         <v>235</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>30.5</v>
+        <v>1203</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24.78</v>
       </c>
     </row>
     <row r="11">
@@ -1200,10 +1841,13 @@
         <v>313</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>1203</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22.79</v>
       </c>
     </row>
     <row r="12">
@@ -1224,10 +1868,13 @@
         <v>456</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>9.06</v>
+        <v>1203</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.35</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1895,13 @@
         <v>441</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>1203</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14.64</v>
       </c>
     </row>
     <row r="14">
@@ -1272,10 +1922,13 @@
         <v>438</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>10.19</v>
+        <v>1203</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.69</v>
       </c>
     </row>
   </sheetData>
@@ -1290,8 +1943,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1326,7 +1979,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -1350,10 +2008,13 @@
         <v>117</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>53.78</v>
+        <v>1612</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.77</v>
       </c>
     </row>
     <row r="3">
@@ -1374,10 +2035,13 @@
         <v>244</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>33.06</v>
+        <v>1612</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30.33</v>
       </c>
     </row>
     <row r="4">
@@ -1398,10 +2062,13 @@
         <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>52.33</v>
+        <v>1612</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.43</v>
       </c>
     </row>
     <row r="5">
@@ -1422,10 +2089,13 @@
         <v>146</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>42.13</v>
+        <v>1612</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="6">
@@ -1446,10 +2116,13 @@
         <v>247</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>32.78</v>
+        <v>1612</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30.26</v>
       </c>
     </row>
     <row r="7">
@@ -1470,10 +2143,13 @@
         <v>453</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>10.96</v>
+        <v>1612</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20.56</v>
       </c>
     </row>
     <row r="8">
@@ -1494,10 +2170,13 @@
         <v>143</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>50.89</v>
+        <v>1612</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.08</v>
       </c>
     </row>
     <row r="9">
@@ -1518,10 +2197,13 @@
         <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>69.09</v>
+        <v>1612</v>
+      </c>
+      <c r="G9" t="n">
+        <v>47.92</v>
       </c>
     </row>
     <row r="10">
@@ -1542,10 +2224,13 @@
         <v>1058</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1612</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.92</v>
       </c>
     </row>
     <row r="11">
@@ -1566,10 +2251,13 @@
         <v>678</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1612</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.43</v>
       </c>
     </row>
     <row r="12">
@@ -1590,10 +2278,13 @@
         <v>1335</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1612</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.46</v>
       </c>
     </row>
     <row r="13">
@@ -1614,10 +2305,13 @@
         <v>359</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>17.93</v>
+        <v>1612</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22.23</v>
       </c>
     </row>
     <row r="14">
@@ -1638,10 +2332,13 @@
         <v>214</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>35.83</v>
+        <v>1612</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1655,8 +2352,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -1691,7 +2388,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -1715,10 +2417,13 @@
         <v>261</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>31.48</v>
+        <v>1576</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32.12</v>
       </c>
     </row>
     <row r="3">
@@ -1739,10 +2444,13 @@
         <v>249</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>32.59</v>
+        <v>1576</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32.41</v>
       </c>
     </row>
     <row r="4">
@@ -1763,10 +2471,13 @@
         <v>243</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>33.15</v>
+        <v>1576</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.56</v>
       </c>
     </row>
     <row r="5">
@@ -1787,10 +2498,13 @@
         <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>82.67</v>
+        <v>1576</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59.9</v>
       </c>
     </row>
     <row r="6">
@@ -1811,10 +2525,13 @@
         <v>300</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>27.87</v>
+        <v>1576</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.16</v>
       </c>
     </row>
     <row r="7">
@@ -1835,10 +2552,13 @@
         <v>728</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1576</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.43</v>
       </c>
     </row>
     <row r="8">
@@ -1859,10 +2579,13 @@
         <v>103</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>64.56</v>
+        <v>1576</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50.36</v>
       </c>
     </row>
     <row r="9">
@@ -1883,10 +2606,13 @@
         <v>97</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>65.33</v>
+        <v>1576</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50.57</v>
       </c>
     </row>
     <row r="10">
@@ -1907,10 +2633,13 @@
         <v>472</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>9.56</v>
+        <v>1576</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.57</v>
       </c>
     </row>
     <row r="11">
@@ -1931,10 +2660,13 @@
         <v>310</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>26.94</v>
+        <v>1576</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30.92</v>
       </c>
     </row>
     <row r="12">
@@ -1955,10 +2687,13 @@
         <v>821</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1576</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.07</v>
       </c>
     </row>
     <row r="13">
@@ -1979,10 +2714,13 @@
         <v>730</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1576</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.4</v>
       </c>
     </row>
     <row r="14">
@@ -2003,10 +2741,13 @@
         <v>1164</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1576</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.03</v>
       </c>
     </row>
   </sheetData>
@@ -2020,8 +2761,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2056,7 +2797,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -2079,9 +2825,12 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
+        <v>1311</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2103,10 +2852,13 @@
         <v>329</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>19.43</v>
+        <v>1311</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20.45</v>
       </c>
     </row>
     <row r="4">
@@ -2127,10 +2879,13 @@
         <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>63.1</v>
+        <v>1311</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43.03</v>
       </c>
     </row>
     <row r="5">
@@ -2151,10 +2906,13 @@
         <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>62.74</v>
+        <v>1311</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42.92</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2933,13 @@
         <v>198</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>38.38</v>
+        <v>1311</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30.9</v>
       </c>
     </row>
     <row r="7">
@@ -2199,10 +2960,13 @@
         <v>537</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>4.57</v>
+        <v>1311</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16.12</v>
       </c>
     </row>
     <row r="8">
@@ -2223,10 +2987,13 @@
         <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>62.38</v>
+        <v>1311</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42.82</v>
       </c>
     </row>
     <row r="9">
@@ -2247,10 +3014,13 @@
         <v>133</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>55.71</v>
+        <v>1311</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40.88</v>
       </c>
     </row>
     <row r="10">
@@ -2271,10 +3041,13 @@
         <v>536</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>4.64</v>
+        <v>1311</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16.14</v>
       </c>
     </row>
     <row r="11">
@@ -2295,10 +3068,13 @@
         <v>252</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>33.24</v>
+        <v>1311</v>
+      </c>
+      <c r="G11" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="12">
@@ -2319,10 +3095,13 @@
         <v>789</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1311</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="13">
@@ -2343,10 +3122,13 @@
         <v>460</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>10.07</v>
+        <v>1311</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17.72</v>
       </c>
     </row>
     <row r="14">
@@ -2366,9 +3148,12 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
+        <v>1311</v>
+      </c>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2383,8 +3168,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2419,7 +3204,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -2443,10 +3233,13 @@
         <v>182</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>43.65</v>
+        <v>1530</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.08</v>
       </c>
     </row>
     <row r="3">
@@ -2467,10 +3260,13 @@
         <v>567</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>2.83</v>
+        <v>1530</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22.91</v>
       </c>
     </row>
     <row r="4">
@@ -2491,10 +3287,13 @@
         <v>169</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>1530</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.46</v>
       </c>
     </row>
     <row r="5">
@@ -2515,10 +3314,13 @@
         <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>66.88</v>
+        <v>1530</v>
+      </c>
+      <c r="G5" t="n">
+        <v>52.23</v>
       </c>
     </row>
     <row r="6">
@@ -2539,10 +3341,13 @@
         <v>1022</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1530</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.07</v>
       </c>
     </row>
     <row r="7">
@@ -2563,10 +3368,13 @@
         <v>1064</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1530</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.55</v>
       </c>
     </row>
     <row r="8">
@@ -2587,10 +3395,13 @@
         <v>239</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>37.71</v>
+        <v>1530</v>
+      </c>
+      <c r="G8" t="n">
+        <v>38.38</v>
       </c>
     </row>
     <row r="9">
@@ -2611,10 +3422,13 @@
         <v>119</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>60.25</v>
+        <v>1530</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50.34</v>
       </c>
     </row>
     <row r="10">
@@ -2635,10 +3449,13 @@
         <v>486</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>11.98</v>
+        <v>1530</v>
+      </c>
+      <c r="G10" t="n">
+        <v>31.05</v>
       </c>
     </row>
     <row r="11">
@@ -2659,10 +3476,13 @@
         <v>1040</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1530</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.75</v>
       </c>
     </row>
     <row r="12">
@@ -2683,10 +3503,13 @@
         <v>786</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1530</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17.71</v>
       </c>
     </row>
     <row r="13">
@@ -2707,10 +3530,13 @@
         <v>265</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>1530</v>
+      </c>
+      <c r="G13" t="n">
+        <v>37.61</v>
       </c>
     </row>
     <row r="14">
@@ -2731,10 +3557,13 @@
         <v>1025</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1530</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.02</v>
       </c>
     </row>
   </sheetData>
@@ -2748,8 +3577,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2784,7 +3613,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -2808,10 +3642,13 @@
         <v>224</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9</v>
+        <v>1495</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.03</v>
       </c>
     </row>
     <row r="3">
@@ -2832,10 +3669,13 @@
         <v>444</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>14.95</v>
+        <v>1495</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28.15</v>
       </c>
     </row>
     <row r="4">
@@ -2856,10 +3696,13 @@
         <v>189</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>49.05</v>
+        <v>1495</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43.71</v>
       </c>
     </row>
     <row r="5">
@@ -2880,10 +3723,13 @@
         <v>257</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>32.76</v>
+        <v>1495</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33.15</v>
       </c>
     </row>
     <row r="6">
@@ -2904,10 +3750,13 @@
         <v>255</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>32.95</v>
+        <v>1495</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33.2</v>
       </c>
     </row>
     <row r="7">
@@ -2928,10 +3777,13 @@
         <v>649</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1495</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -2952,10 +3804,13 @@
         <v>544</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>5.43</v>
+        <v>1495</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25.47</v>
       </c>
     </row>
     <row r="9">
@@ -2976,10 +3831,13 @@
         <v>186</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>49.4</v>
+        <v>1495</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43.81</v>
       </c>
     </row>
     <row r="10">
@@ -3000,10 +3858,13 @@
         <v>871</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1495</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.54</v>
       </c>
     </row>
     <row r="11">
@@ -3024,10 +3885,13 @@
         <v>472</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>12.29</v>
+        <v>1495</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27.4</v>
       </c>
     </row>
     <row r="12">
@@ -3048,10 +3912,13 @@
         <v>1119</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1495</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.04</v>
       </c>
     </row>
     <row r="13">
@@ -3072,10 +3939,13 @@
         <v>475</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>1495</v>
+      </c>
+      <c r="G13" t="n">
+        <v>27.32</v>
       </c>
     </row>
     <row r="14">
@@ -3096,10 +3966,13 @@
         <v>482</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>11.33</v>
+        <v>1495</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27.13</v>
       </c>
     </row>
   </sheetData>
@@ -3113,8 +3986,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -3149,7 +4022,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -3173,10 +4051,13 @@
         <v>151</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>46.88</v>
+        <v>1426</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.42</v>
       </c>
     </row>
     <row r="3">
@@ -3197,10 +4078,13 @@
         <v>214</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>40.31</v>
+        <v>1426</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32.72</v>
       </c>
     </row>
     <row r="4">
@@ -3221,10 +4105,13 @@
         <v>217</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>1426</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.64</v>
       </c>
     </row>
     <row r="5">
@@ -3245,10 +4132,13 @@
         <v>441</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>13.33</v>
+        <v>1426</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21.28</v>
       </c>
     </row>
     <row r="6">
@@ -3269,10 +4159,13 @@
         <v>337</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>1426</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23.52</v>
       </c>
     </row>
     <row r="7">
@@ -3293,10 +4186,13 @@
         <v>368</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>19.42</v>
+        <v>1426</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22.85</v>
       </c>
     </row>
     <row r="8">
@@ -3317,10 +4213,13 @@
         <v>227</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96</v>
+        <v>1426</v>
+      </c>
+      <c r="G8" t="n">
+        <v>32.37</v>
       </c>
     </row>
     <row r="9">
@@ -3341,10 +4240,13 @@
         <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>97.67</v>
+        <v>1426</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60.93</v>
       </c>
     </row>
     <row r="10">
@@ -3365,10 +4267,13 @@
         <v>720</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1426</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11.44</v>
       </c>
     </row>
     <row r="11">
@@ -3389,10 +4294,13 @@
         <v>442</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>13.25</v>
+        <v>1426</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21.25</v>
       </c>
     </row>
     <row r="12">
@@ -3413,10 +4321,13 @@
         <v>921</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1426</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.19</v>
       </c>
     </row>
     <row r="13">
@@ -3437,10 +4348,13 @@
         <v>155</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>46.46</v>
+        <v>1426</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.31</v>
       </c>
     </row>
     <row r="14">
@@ -3461,10 +4375,13 @@
         <v>362</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>19.92</v>
+        <v>1426</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.98</v>
       </c>
     </row>
   </sheetData>
@@ -3478,8 +4395,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -3514,7 +4431,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -3538,10 +4460,13 @@
         <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>68.95999999999999</v>
+        <v>1405</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51.24</v>
       </c>
     </row>
     <row r="3">
@@ -3562,10 +4487,13 @@
         <v>284</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>29.35</v>
+        <v>1405</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30.71</v>
       </c>
     </row>
     <row r="4">
@@ -3586,10 +4514,13 @@
         <v>145</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>50.67</v>
+        <v>1405</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41.42</v>
       </c>
     </row>
     <row r="5">
@@ -3610,10 +4541,13 @@
         <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>52.89</v>
+        <v>1405</v>
+      </c>
+      <c r="G5" t="n">
+        <v>42.08</v>
       </c>
     </row>
     <row r="6">
@@ -3634,10 +4568,13 @@
         <v>482</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>8.81</v>
+        <v>1405</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20.24</v>
       </c>
     </row>
     <row r="7">
@@ -3658,10 +4595,13 @@
         <v>594</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>0.52</v>
+        <v>1405</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.78</v>
       </c>
     </row>
     <row r="8">
@@ -3682,10 +4622,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>55.67</v>
+        <v>1405</v>
+      </c>
+      <c r="G8" t="n">
+        <v>42.9</v>
       </c>
     </row>
     <row r="9">
@@ -3706,10 +4649,13 @@
         <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>67.8</v>
+        <v>1405</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50.9</v>
       </c>
     </row>
     <row r="10">
@@ -3730,10 +4676,13 @@
         <v>300</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>27.87</v>
+        <v>1405</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30.28</v>
       </c>
     </row>
     <row r="11">
@@ -3754,10 +4703,13 @@
         <v>740</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1405</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14.59</v>
       </c>
     </row>
     <row r="12">
@@ -3778,10 +4730,13 @@
         <v>810</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1405</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13.05</v>
       </c>
     </row>
     <row r="13">
@@ -3802,10 +4757,13 @@
         <v>152</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>49.89</v>
+        <v>1405</v>
+      </c>
+      <c r="G13" t="n">
+        <v>41.19</v>
       </c>
     </row>
     <row r="14">
@@ -3826,10 +4784,13 @@
         <v>1247</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1405</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>
@@ -3844,8 +4805,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -3880,7 +4841,12 @@
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>max_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>得分</t>
         </is>
@@ -3904,10 +4870,13 @@
         <v>196</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>37.5</v>
+        <v>1442</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.31</v>
       </c>
     </row>
     <row r="3">
@@ -3928,10 +4897,13 @@
         <v>279</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>23.85</v>
+        <v>1442</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.35</v>
       </c>
     </row>
     <row r="4">
@@ -3952,10 +4924,13 @@
         <v>257</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>31.85</v>
+        <v>1442</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37.38</v>
       </c>
     </row>
     <row r="5">
@@ -3976,10 +4951,13 @@
         <v>272</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>24.37</v>
+        <v>1442</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29.53</v>
       </c>
     </row>
     <row r="6">
@@ -4000,10 +4978,13 @@
         <v>564</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>2.74</v>
+        <v>1442</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.17</v>
       </c>
     </row>
     <row r="7">
@@ -4024,10 +5005,13 @@
         <v>905</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1442</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.18</v>
       </c>
     </row>
     <row r="8">
@@ -4048,10 +5032,13 @@
         <v>572</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>2.15</v>
+        <v>1442</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21.96</v>
       </c>
     </row>
     <row r="9">
@@ -4072,10 +5059,13 @@
         <v>125</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>44.07</v>
+        <v>1442</v>
+      </c>
+      <c r="G9" t="n">
+        <v>41.55</v>
       </c>
     </row>
     <row r="10">
@@ -4096,10 +5086,13 @@
         <v>552</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>3.63</v>
+        <v>1442</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22.47</v>
       </c>
     </row>
     <row r="11">
@@ -4120,10 +5113,13 @@
         <v>476</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>9.26</v>
+        <v>1442</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24.39</v>
       </c>
     </row>
     <row r="12">
@@ -4144,10 +5140,13 @@
         <v>1062</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1442</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.21</v>
       </c>
     </row>
     <row r="13">
@@ -4168,10 +5167,13 @@
         <v>706</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1442</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.94</v>
       </c>
     </row>
     <row r="14">
@@ -4192,10 +5194,13 @@
         <v>1099</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1442</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.51</v>
       </c>
     </row>
   </sheetData>
